--- a/data/trans_dic/LAWTONB_2R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R3-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia moderada o superior</t>
+          <t>Población con dependencia moderada o superior (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 28,49</t>
+          <t>5,35; 29,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,42; 38,6</t>
+          <t>13,03; 38,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,08; 35,83</t>
+          <t>11,88; 36,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,49; 39,61</t>
+          <t>19,33; 38,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 31,33</t>
+          <t>6,3; 33,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,96; 62,56</t>
+          <t>32,96; 61,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,92; 55,1</t>
+          <t>25,58; 55,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,78; 47,89</t>
+          <t>31,28; 48,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,34; 25,82</t>
+          <t>9,87; 27,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 47,56</t>
+          <t>26,16; 45,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,43; 41,72</t>
+          <t>21,89; 43,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,03; 41,23</t>
+          <t>27,97; 41,6</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 21,51</t>
+          <t>4,47; 21,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,24; 31,83</t>
+          <t>10,88; 31,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 16,26</t>
+          <t>4,69; 16,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 20,89</t>
+          <t>6,51; 20,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 21,94</t>
+          <t>7,45; 21,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,3; 42,29</t>
+          <t>23,04; 42,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,5; 34,33</t>
+          <t>16,44; 34,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,36; 38,51</t>
+          <t>26,43; 38,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,13; 18,32</t>
+          <t>7,77; 18,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,01; 34,96</t>
+          <t>20,84; 35,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,58; 24,86</t>
+          <t>12,94; 24,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,47; 30,03</t>
+          <t>19,85; 29,59</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 21,36</t>
+          <t>3,52; 19,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,95; 37,72</t>
+          <t>13,42; 38,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 22,09</t>
+          <t>6,32; 22,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,59; 32,23</t>
+          <t>17,09; 32,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,44; 31,9</t>
+          <t>12,3; 29,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,07; 34,53</t>
+          <t>15,44; 35,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 22,68</t>
+          <t>4,82; 22,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,83; 40,25</t>
+          <t>25,67; 40,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 23,22</t>
+          <t>10,71; 23,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,98; 31,47</t>
+          <t>17,17; 33,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 19,35</t>
+          <t>7,42; 18,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,59; 34,01</t>
+          <t>23,37; 33,92</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 14,35</t>
+          <t>1,63; 14,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,59; 38,28</t>
+          <t>15,22; 37,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,9; 29,8</t>
+          <t>11,74; 28,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 26,06</t>
+          <t>12,39; 26,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,49; 34,62</t>
+          <t>13,8; 34,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,84; 37,91</t>
+          <t>17,85; 37,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,95; 30,85</t>
+          <t>11,66; 30,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,98; 28,18</t>
+          <t>17,76; 28,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 24,04</t>
+          <t>10,47; 23,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,45; 34,87</t>
+          <t>19,48; 34,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,05; 26,6</t>
+          <t>13,31; 26,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 25,52</t>
+          <t>16,97; 25,23</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,8; 44,55</t>
+          <t>13,36; 43,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,6; 38,0</t>
+          <t>9,05; 39,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 20,43</t>
+          <t>3,74; 20,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,85; 32,52</t>
+          <t>12,57; 32,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 45,8</t>
+          <t>17,76; 46,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 42,79</t>
+          <t>18,01; 42,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,25; 52,09</t>
+          <t>24,3; 51,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,17; 32,42</t>
+          <t>18,24; 30,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,05; 39,26</t>
+          <t>18,78; 40,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,24; 36,62</t>
+          <t>17,62; 36,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,05; 35,39</t>
+          <t>16,2; 34,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,19; 29,41</t>
+          <t>18,41; 30,06</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,1; 30,08</t>
+          <t>9,68; 30,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,49; 43,18</t>
+          <t>16,66; 43,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,48; 38,22</t>
+          <t>15,4; 37,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,32; 40,06</t>
+          <t>24,47; 39,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,41; 27,11</t>
+          <t>9,82; 28,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,18; 38,89</t>
+          <t>16,89; 38,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,94; 42,35</t>
+          <t>18,36; 43,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,28; 44,05</t>
+          <t>30,72; 45,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,07; 25,85</t>
+          <t>11,06; 24,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,21; 35,96</t>
+          <t>20,11; 36,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,26; 36,12</t>
+          <t>19,42; 36,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,46; 40,51</t>
+          <t>29,18; 39,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 15,12</t>
+          <t>3,95; 14,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,73; 31,75</t>
+          <t>14,25; 31,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,32; 24,83</t>
+          <t>10,64; 24,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 15,31</t>
+          <t>5,91; 15,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 20,04</t>
+          <t>7,81; 20,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,49; 31,29</t>
+          <t>16,47; 31,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,1; 36,5</t>
+          <t>20,26; 36,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 28,67</t>
+          <t>2,47; 28,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 16,07</t>
+          <t>7,0; 15,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,84; 28,69</t>
+          <t>17,55; 28,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,79; 29,2</t>
+          <t>18,7; 29,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 19,91</t>
+          <t>3,3; 19,95</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,52; 23,55</t>
+          <t>10,76; 23,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,47; 19,25</t>
+          <t>5,68; 19,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,08; 19,8</t>
+          <t>7,77; 19,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,09; 11,68</t>
+          <t>4,93; 11,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,62; 28,09</t>
+          <t>14,7; 27,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,94; 24,62</t>
+          <t>12,22; 23,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,65; 23,28</t>
+          <t>10,63; 23,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,68; 26,77</t>
+          <t>17,99; 27,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,4; 24,26</t>
+          <t>14,44; 24,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,95; 20,28</t>
+          <t>10,84; 19,94</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,98; 19,37</t>
+          <t>10,63; 19,47</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,15; 19,12</t>
+          <t>13,07; 19,0</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,24; 15,93</t>
+          <t>10,21; 16,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,15; 24,86</t>
+          <t>17,41; 24,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,58; 17,89</t>
+          <t>12,23; 17,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,43; 18,91</t>
+          <t>14,37; 19,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,58; 21,8</t>
+          <t>15,61; 21,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,05; 29,46</t>
+          <t>23,26; 30,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,19; 26,8</t>
+          <t>20,58; 27,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,7; 28,99</t>
+          <t>12,0; 29,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,09; 18,44</t>
+          <t>13,97; 18,37</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21,25; 26,2</t>
+          <t>21,38; 26,34</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,88; 22,44</t>
+          <t>17,73; 22,37</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,22; 23,78</t>
+          <t>13,69; 23,87</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia moderada o superior</t>
+          <t>Población con dependencia moderada o superior (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2544; 10080</t>
+          <t>1894; 10480</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5499; 17092</t>
+          <t>5768; 17124</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4699; 13938</t>
+          <t>4620; 14346</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10336; 22144</t>
+          <t>10806; 21735</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2426; 12291</t>
+          <t>2471; 13325</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16605; 30590</t>
+          <t>16114; 30278</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12307; 27217</t>
+          <t>12634; 27651</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19517; 30366</t>
+          <t>19837; 30639</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6973; 19263</t>
+          <t>7362; 20392</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24876; 44317</t>
+          <t>24378; 42737</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18918; 36829</t>
+          <t>19330; 38416</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33448; 49188</t>
+          <t>33371; 49637</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3679; 14337</t>
+          <t>2980; 14294</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8899; 25212</t>
+          <t>8614; 25325</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4022; 14198</t>
+          <t>4096; 14718</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5192; 16679</t>
+          <t>5194; 16557</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7155; 21470</t>
+          <t>7291; 20897</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23791; 43173</t>
+          <t>23525; 43421</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19008; 39559</t>
+          <t>18943; 40163</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33860; 49471</t>
+          <t>33957; 50079</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13379; 30142</t>
+          <t>12785; 30171</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36278; 63373</t>
+          <t>37775; 63623</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25473; 50351</t>
+          <t>26204; 50428</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42637; 62555</t>
+          <t>41343; 61637</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1924; 10880</t>
+          <t>1793; 9950</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7219; 21029</t>
+          <t>7481; 21680</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3845; 14040</t>
+          <t>4016; 14184</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12192; 23686</t>
+          <t>12557; 23645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10390; 26639</t>
+          <t>10272; 24793</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12053; 27614</t>
+          <t>12348; 28143</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3808; 18123</t>
+          <t>3852; 18032</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22438; 34957</t>
+          <t>22295; 35490</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13456; 31216</t>
+          <t>14395; 32080</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23037; 42701</t>
+          <t>23303; 45513</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10712; 27760</t>
+          <t>10641; 26556</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37819; 54530</t>
+          <t>37471; 54383</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>848; 7910</t>
+          <t>897; 8132</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9979; 24511</t>
+          <t>9745; 24290</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7053; 19286</t>
+          <t>7595; 18646</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8898; 19006</t>
+          <t>9035; 19618</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11510; 25729</t>
+          <t>10257; 25654</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16119; 32438</t>
+          <t>15277; 32362</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10023; 28254</t>
+          <t>10680; 28191</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18631; 29206</t>
+          <t>18409; 29301</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14624; 31114</t>
+          <t>13557; 29976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29093; 52159</t>
+          <t>29138; 51348</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20402; 41570</t>
+          <t>20809; 41732</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30337; 45068</t>
+          <t>29970; 44552</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4049; 13074</t>
+          <t>3922; 12697</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3036; 12013</t>
+          <t>2861; 12531</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1609; 8595</t>
+          <t>1576; 8656</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4823; 11321</t>
+          <t>4377; 11356</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7081; 18893</t>
+          <t>7323; 19055</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8807; 21331</t>
+          <t>8980; 21268</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11243; 26323</t>
+          <t>12279; 25896</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10703; 19094</t>
+          <t>10740; 18175</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13451; 27717</t>
+          <t>13255; 28639</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13227; 29830</t>
+          <t>14354; 30076</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14866; 32774</t>
+          <t>15006; 32117</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17047; 27560</t>
+          <t>17252; 28167</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3824; 14195</t>
+          <t>4568; 14345</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9569; 22348</t>
+          <t>8620; 22676</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7498; 18518</t>
+          <t>7460; 18295</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14053; 24142</t>
+          <t>14745; 23771</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5914; 19062</t>
+          <t>6907; 20160</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12764; 27302</t>
+          <t>11856; 27261</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12088; 28542</t>
+          <t>12374; 29591</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19520; 28393</t>
+          <t>19804; 29170</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13010; 30371</t>
+          <t>12998; 29202</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24654; 43856</t>
+          <t>24530; 44539</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22309; 41840</t>
+          <t>22498; 42733</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>36748; 50531</t>
+          <t>36388; 49777</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4235; 16014</t>
+          <t>4189; 15356</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16538; 35645</t>
+          <t>15995; 35476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12695; 27855</t>
+          <t>11934; 28027</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6607; 18762</t>
+          <t>7245; 19276</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8735; 23476</t>
+          <t>9147; 23764</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23405; 44421</t>
+          <t>23386; 44697</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31151; 53885</t>
+          <t>29909; 53694</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9654; 96781</t>
+          <t>8352; 96787</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16381; 35835</t>
+          <t>15618; 33808</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>45342; 72943</t>
+          <t>44611; 72996</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46208; 75868</t>
+          <t>48575; 76367</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15012; 91616</t>
+          <t>15191; 91812</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11769; 26347</t>
+          <t>12035; 26172</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6609; 23241</t>
+          <t>6864; 23348</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10840; 26563</t>
+          <t>10428; 25723</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7359; 16889</t>
+          <t>7130; 17219</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>22399; 43046</t>
+          <t>22525; 42491</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19627; 40481</t>
+          <t>20097; 39289</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18782; 41046</t>
+          <t>18747; 41912</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>32872; 49775</t>
+          <t>33459; 50223</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38188; 64312</t>
+          <t>38272; 64776</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31223; 57824</t>
+          <t>30927; 56859</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34094; 60145</t>
+          <t>33011; 60437</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>43460; 63218</t>
+          <t>43211; 62810</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>51447; 80020</t>
+          <t>51284; 80384</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>95990; 139114</t>
+          <t>97438; 137651</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>74368; 105805</t>
+          <t>72292; 106074</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>92960; 121889</t>
+          <t>92603; 123621</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>105422; 147546</t>
+          <t>105642; 146624</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>171276; 218887</t>
+          <t>172810; 223623</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>157095; 208522</t>
+          <t>160121; 212250</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>120404; 298399</t>
+          <t>123513; 300052</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>166149; 217492</t>
+          <t>164711; 216682</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>276862; 341262</t>
+          <t>278494; 343070</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>244869; 307275</t>
+          <t>242771; 306347</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>237958; 397968</t>
+          <t>229064; 399571</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/LAWTONB_2R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R3-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 29,62</t>
+          <t>6,9; 28,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,03; 38,67</t>
+          <t>12,85; 39,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,88; 36,88</t>
+          <t>10,35; 34,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,33; 38,88</t>
+          <t>19,23; 38,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 33,96</t>
+          <t>6,3; 33,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,96; 61,93</t>
+          <t>32,3; 62,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,58; 55,98</t>
+          <t>23,6; 54,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,28; 48,32</t>
+          <t>31,08; 47,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,87; 27,33</t>
+          <t>9,18; 27,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,16; 45,87</t>
+          <t>25,4; 46,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,89; 43,51</t>
+          <t>21,78; 41,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,97; 41,6</t>
+          <t>27,29; 40,71</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 21,45</t>
+          <t>5,46; 21,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,88; 31,97</t>
+          <t>10,79; 32,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 16,86</t>
+          <t>4,84; 16,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 20,74</t>
+          <t>6,45; 20,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 21,35</t>
+          <t>7,38; 22,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,04; 42,53</t>
+          <t>22,46; 42,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,44; 34,86</t>
+          <t>17,11; 35,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,43; 38,98</t>
+          <t>27,4; 39,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 18,34</t>
+          <t>7,81; 18,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,84; 35,09</t>
+          <t>20,96; 34,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,94; 24,9</t>
+          <t>12,66; 24,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,85; 29,59</t>
+          <t>20,25; 29,87</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 19,53</t>
+          <t>3,65; 19,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 38,89</t>
+          <t>13,11; 37,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 22,32</t>
+          <t>6,42; 21,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,09; 32,17</t>
+          <t>17,37; 32,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,3; 29,68</t>
+          <t>11,93; 30,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,44; 35,19</t>
+          <t>15,5; 34,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 22,57</t>
+          <t>5,7; 21,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,67; 40,86</t>
+          <t>25,8; 41,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 23,86</t>
+          <t>10,44; 23,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,17; 33,54</t>
+          <t>17,35; 31,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 18,51</t>
+          <t>7,44; 18,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,37; 33,92</t>
+          <t>23,98; 34,57</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 14,75</t>
+          <t>1,58; 14,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,22; 37,94</t>
+          <t>15,2; 37,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,74; 28,81</t>
+          <t>11,89; 29,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 26,9</t>
+          <t>11,84; 24,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,8; 34,52</t>
+          <t>15,12; 34,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,85; 37,82</t>
+          <t>19,14; 38,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,66; 30,78</t>
+          <t>10,64; 30,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,76; 28,27</t>
+          <t>17,43; 27,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 23,16</t>
+          <t>11,01; 23,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,48; 34,32</t>
+          <t>19,97; 34,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 26,7</t>
+          <t>12,8; 27,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,97; 25,23</t>
+          <t>16,7; 24,96</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,36; 43,27</t>
+          <t>14,41; 43,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 39,64</t>
+          <t>7,54; 41,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 20,57</t>
+          <t>3,78; 20,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,57; 32,62</t>
+          <t>13,65; 32,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,76; 46,2</t>
+          <t>17,34; 47,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,01; 42,66</t>
+          <t>16,33; 40,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,3; 51,25</t>
+          <t>22,57; 51,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,24; 30,86</t>
+          <t>18,05; 32,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,78; 40,57</t>
+          <t>18,33; 40,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,62; 36,92</t>
+          <t>17,15; 37,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,2; 34,68</t>
+          <t>15,84; 33,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,41; 30,06</t>
+          <t>18,1; 29,08</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,68; 30,4</t>
+          <t>7,94; 29,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,66; 43,81</t>
+          <t>16,8; 42,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,4; 37,76</t>
+          <t>13,71; 35,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,47; 39,45</t>
+          <t>23,49; 39,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,82; 28,67</t>
+          <t>9,05; 27,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,89; 38,83</t>
+          <t>16,93; 38,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,36; 43,91</t>
+          <t>17,26; 41,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,72; 45,25</t>
+          <t>29,7; 44,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,06; 24,85</t>
+          <t>11,32; 25,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,11; 36,52</t>
+          <t>20,22; 36,39</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,42; 36,89</t>
+          <t>18,96; 36,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,18; 39,91</t>
+          <t>29,27; 39,8</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 14,5</t>
+          <t>4,1; 14,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,25; 31,6</t>
+          <t>15,17; 31,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,64; 24,98</t>
+          <t>11,11; 25,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 15,73</t>
+          <t>5,72; 15,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,81; 20,29</t>
+          <t>7,76; 20,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,47; 31,49</t>
+          <t>16,76; 32,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,26; 36,37</t>
+          <t>20,18; 35,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 28,67</t>
+          <t>21,62; 33,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,0; 15,16</t>
+          <t>7,04; 15,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,55; 28,71</t>
+          <t>17,61; 28,79</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,7; 29,39</t>
+          <t>17,82; 28,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 19,95</t>
+          <t>15,16; 22,55</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,76; 23,39</t>
+          <t>10,57; 24,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,68; 19,34</t>
+          <t>5,54; 19,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,77; 19,17</t>
+          <t>7,54; 19,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,91</t>
+          <t>5,22; 12,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,7; 27,73</t>
+          <t>14,28; 28,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,22; 23,9</t>
+          <t>12,39; 24,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,63; 23,77</t>
+          <t>10,94; 22,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,99; 27,01</t>
+          <t>18,78; 28,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,44; 24,43</t>
+          <t>14,27; 24,03</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,84; 19,94</t>
+          <t>10,91; 20,32</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,63; 19,47</t>
+          <t>10,76; 19,73</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,07; 19,0</t>
+          <t>13,77; 19,7</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,21; 16,0</t>
+          <t>10,51; 16,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,41; 24,6</t>
+          <t>17,04; 24,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,23; 17,94</t>
+          <t>12,53; 17,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,37; 19,18</t>
+          <t>13,78; 18,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,61; 21,66</t>
+          <t>15,63; 21,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,26; 30,1</t>
+          <t>23,09; 29,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,58; 27,28</t>
+          <t>20,29; 27,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,0; 29,15</t>
+          <t>26,28; 30,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,97; 18,37</t>
+          <t>13,99; 18,29</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21,38; 26,34</t>
+          <t>21,61; 26,27</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,73; 22,37</t>
+          <t>17,67; 22,14</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,69; 23,87</t>
+          <t>21,4; 24,62</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15992</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25021</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41013</t>
+          <t>42665</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1894; 10480</t>
+          <t>2442; 10026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5768; 17124</t>
+          <t>5689; 17412</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4620; 14346</t>
+          <t>4025; 13384</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10806; 21735</t>
+          <t>11719; 23513</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2471; 13325</t>
+          <t>2473; 13114</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16114; 30278</t>
+          <t>15795; 30372</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12634; 27651</t>
+          <t>11657; 26958</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19837; 30639</t>
+          <t>20289; 31297</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7362; 20392</t>
+          <t>6853; 20154</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24378; 42737</t>
+          <t>23670; 43014</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19330; 38416</t>
+          <t>19233; 36746</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33371; 49637</t>
+          <t>34443; 51387</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>10299</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41852</t>
+          <t>44693</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51448</t>
+          <t>54992</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2980; 14294</t>
+          <t>3637; 14447</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8614; 25325</t>
+          <t>8547; 25645</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4096; 14718</t>
+          <t>4222; 14679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5194; 16557</t>
+          <t>5638; 17549</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7291; 20897</t>
+          <t>7222; 21764</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23525; 43421</t>
+          <t>22928; 43841</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18943; 40163</t>
+          <t>19717; 40667</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33957; 50079</t>
+          <t>36920; 53777</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12785; 30171</t>
+          <t>12851; 30417</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37775; 63623</t>
+          <t>38001; 63344</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26204; 50428</t>
+          <t>25646; 50280</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41343; 61637</t>
+          <t>44986; 66374</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>28198</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45913</t>
+          <t>45582</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1793; 9950</t>
+          <t>1859; 10121</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7481; 21680</t>
+          <t>7309; 20939</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4016; 14184</t>
+          <t>4077; 13964</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12557; 23645</t>
+          <t>12555; 23396</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10272; 24793</t>
+          <t>9960; 25649</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12348; 28143</t>
+          <t>12396; 27701</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3852; 18032</t>
+          <t>4551; 17529</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22295; 35490</t>
+          <t>22000; 35036</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14395; 32080</t>
+          <t>14035; 31405</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23303; 45513</t>
+          <t>23541; 43080</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10641; 26556</t>
+          <t>10677; 27040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37471; 54383</t>
+          <t>37782; 54468</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>39390</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>897; 8132</t>
+          <t>874; 8068</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9745; 24290</t>
+          <t>9731; 23901</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7595; 18646</t>
+          <t>7693; 19055</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9035; 19618</t>
+          <t>9639; 20172</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10257; 25654</t>
+          <t>11234; 25746</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15277; 32362</t>
+          <t>16380; 32807</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10680; 28191</t>
+          <t>9746; 27669</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18409; 29301</t>
+          <t>19256; 30207</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13557; 29976</t>
+          <t>14249; 30267</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29138; 51348</t>
+          <t>29870; 52116</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20809; 41732</t>
+          <t>20005; 42331</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29970; 44552</t>
+          <t>32038; 47902</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>14904</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21838</t>
+          <t>22581</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3922; 12697</t>
+          <t>4230; 12747</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2861; 12531</t>
+          <t>2385; 13044</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1576; 8656</t>
+          <t>1589; 8468</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4377; 11356</t>
+          <t>4982; 11848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7323; 19055</t>
+          <t>7154; 19485</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8980; 21268</t>
+          <t>8140; 20418</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12279; 25896</t>
+          <t>11408; 26162</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10740; 18175</t>
+          <t>11040; 19595</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13255; 28639</t>
+          <t>12940; 28765</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14354; 30076</t>
+          <t>13972; 30236</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15006; 32117</t>
+          <t>14670; 31419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17252; 28167</t>
+          <t>17677; 28400</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>42934</t>
+          <t>43324</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4568; 14345</t>
+          <t>3750; 13717</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8620; 22676</t>
+          <t>8697; 22203</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7460; 18295</t>
+          <t>6641; 17096</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14745; 23771</t>
+          <t>14149; 23515</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6907; 20160</t>
+          <t>6360; 19447</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11856; 27261</t>
+          <t>11885; 27246</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12374; 29591</t>
+          <t>11632; 28291</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19804; 29170</t>
+          <t>19745; 29861</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12998; 29202</t>
+          <t>13299; 29504</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24530; 44539</t>
+          <t>24658; 44382</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22498; 42733</t>
+          <t>21968; 42615</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>36388; 49777</t>
+          <t>37083; 50431</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>43951</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>47777</t>
+          <t>58552</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4189; 15356</t>
+          <t>4344; 15813</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15995; 35476</t>
+          <t>17034; 35540</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11934; 28027</t>
+          <t>12465; 28272</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7245; 19276</t>
+          <t>8612; 23488</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9147; 23764</t>
+          <t>9088; 23902</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23386; 44697</t>
+          <t>23788; 45484</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29909; 53694</t>
+          <t>29796; 53062</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8352; 96787</t>
+          <t>35215; 54221</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15618; 33808</t>
+          <t>15704; 34714</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44611; 72996</t>
+          <t>44778; 73182</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48575; 76367</t>
+          <t>46301; 74295</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15191; 91812</t>
+          <t>47525; 70663</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>41462</t>
+          <t>48600</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>52784</t>
+          <t>61833</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12035; 26172</t>
+          <t>11825; 27363</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6864; 23348</t>
+          <t>6694; 23331</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10428; 25723</t>
+          <t>10113; 26362</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7130; 17219</t>
+          <t>8394; 20075</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>22525; 42491</t>
+          <t>21882; 42918</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20097; 39289</t>
+          <t>20372; 41012</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18747; 41912</t>
+          <t>19294; 40272</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33459; 50223</t>
+          <t>39785; 59812</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38272; 64776</t>
+          <t>37843; 63702</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>30927; 56859</t>
+          <t>31125; 57942</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33011; 60437</t>
+          <t>33401; 61257</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>43211; 62810</t>
+          <t>51308; 73431</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>106631</t>
+          <t>113539</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>234077</t>
+          <t>255382</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>340708</t>
+          <t>368920</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>51284; 80384</t>
+          <t>52804; 81300</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>97438; 137651</t>
+          <t>95353; 138893</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>72292; 106074</t>
+          <t>74075; 106225</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>92603; 123621</t>
+          <t>97888; 130066</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>105642; 146624</t>
+          <t>105823; 147711</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>172810; 223623</t>
+          <t>171588; 219962</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>160121; 212250</t>
+          <t>157849; 210046</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>123513; 300052</t>
+          <t>236056; 274210</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>164711; 216682</t>
+          <t>164992; 215710</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>278494; 343070</t>
+          <t>281438; 342188</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>242771; 306347</t>
+          <t>241978; 303179</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>229064; 399571</t>
+          <t>344204; 396063</t>
         </is>
       </c>
     </row>
